--- a/originales/respuestas/2025/01. Calificadas/bucle p11/Lotería De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p11/Lotería De Bogotá.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Entidad" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="p1" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="GeZHBmCQjhPCiTnxETYt3co1prmXnLH6j2k7d5+cLls="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="HoXGeYWlb6x2s390h+puxib4aLcqXEoWZFL/6zF+WZk="/>
     </ext>
   </extLst>
 </workbook>
@@ -226,6 +227,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -424,6 +429,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>

--- a/originales/respuestas/2025/01. Calificadas/bucle p11/Lotería De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p11/Lotería De Bogotá.xlsx
@@ -17,7 +17,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+  <si>
+    <t>Entidad</t>
+  </si>
   <si>
     <t>Tipo</t>
   </si>
@@ -204,7 +207,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -452,99 +455,101 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4">
         <v>5.9643642E7</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="5">
         <v>2.0</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="5">
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="5">
         <v>2.0</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2" s="5">
         <v>3.0</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P2" s="5">
         <v>2.0</v>
@@ -553,47 +558,47 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4">
         <v>5964.0</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="5">
         <v>2.0</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="5">
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3" s="5">
         <v>2.0</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3" s="5">
         <v>4.0</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P3" s="5">
         <v>2.0</v>
